--- a/workshop/da88ad747a.xlsx
+++ b/workshop/da88ad747a.xlsx
@@ -512,7 +512,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>问题类型：倒闭 / 关停　地区：江苏　内容价值：★92.5　总时长：75.8 秒　镜次：33</t>
+          <t>问题类型：倒闭 / 关停　地区：江苏　内容价值：★92.5　总时长：75.9 秒　镜次：33</t>
         </is>
       </c>
     </row>
@@ -595,10 +595,10 @@
         <v>0</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="E5" s="6" t="inlineStr">
         <is>
@@ -644,10 +644,10 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="D6" s="5" t="n">
         <v>1.2</v>
@@ -696,10 +696,10 @@
         </is>
       </c>
       <c r="B7" s="7" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="C7" s="7" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="D7" s="7" t="n">
         <v>1.9</v>
@@ -744,10 +744,10 @@
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="C8" s="7" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="D8" s="7" t="n">
         <v>1.5</v>
@@ -792,10 +792,10 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="C9" s="7" t="n">
-        <v>8</v>
+        <v>8.1</v>
       </c>
       <c r="D9" s="7" t="n">
         <v>2.6</v>
@@ -840,10 +840,10 @@
         </is>
       </c>
       <c r="B10" s="7" t="n">
-        <v>8</v>
+        <v>8.1</v>
       </c>
       <c r="C10" s="7" t="n">
-        <v>9.6</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="D10" s="7" t="n">
         <v>1.6</v>
@@ -888,10 +888,10 @@
         </is>
       </c>
       <c r="B11" s="7" t="n">
-        <v>9.6</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="C11" s="7" t="n">
-        <v>12.5</v>
+        <v>12.6</v>
       </c>
       <c r="D11" s="7" t="n">
         <v>2.9</v>
@@ -944,10 +944,10 @@
         </is>
       </c>
       <c r="B12" s="7" t="n">
-        <v>12.5</v>
+        <v>12.6</v>
       </c>
       <c r="C12" s="7" t="n">
-        <v>15.9</v>
+        <v>16</v>
       </c>
       <c r="D12" s="7" t="n">
         <v>3.4</v>
@@ -992,10 +992,10 @@
         </is>
       </c>
       <c r="B13" s="7" t="n">
-        <v>15.9</v>
+        <v>16</v>
       </c>
       <c r="C13" s="7" t="n">
-        <v>18.8</v>
+        <v>18.9</v>
       </c>
       <c r="D13" s="7" t="n">
         <v>2.9</v>
@@ -1040,10 +1040,10 @@
         </is>
       </c>
       <c r="B14" s="7" t="n">
-        <v>18.8</v>
+        <v>18.9</v>
       </c>
       <c r="C14" s="7" t="n">
-        <v>20.6</v>
+        <v>20.7</v>
       </c>
       <c r="D14" s="7" t="n">
         <v>1.8</v>
@@ -1088,10 +1088,10 @@
         </is>
       </c>
       <c r="B15" s="7" t="n">
-        <v>20.6</v>
+        <v>20.7</v>
       </c>
       <c r="C15" s="7" t="n">
-        <v>22.4</v>
+        <v>22.5</v>
       </c>
       <c r="D15" s="7" t="n">
         <v>1.8</v>
@@ -1136,10 +1136,10 @@
         </is>
       </c>
       <c r="B16" s="7" t="n">
-        <v>22.4</v>
+        <v>22.5</v>
       </c>
       <c r="C16" s="7" t="n">
-        <v>24.9</v>
+        <v>25</v>
       </c>
       <c r="D16" s="7" t="n">
         <v>2.5</v>
@@ -1184,10 +1184,10 @@
         </is>
       </c>
       <c r="B17" s="7" t="n">
-        <v>24.9</v>
+        <v>25</v>
       </c>
       <c r="C17" s="7" t="n">
-        <v>26.8</v>
+        <v>26.9</v>
       </c>
       <c r="D17" s="7" t="n">
         <v>1.9</v>
@@ -1232,10 +1232,10 @@
         </is>
       </c>
       <c r="B18" s="7" t="n">
-        <v>26.8</v>
+        <v>26.9</v>
       </c>
       <c r="C18" s="7" t="n">
-        <v>28.6</v>
+        <v>28.7</v>
       </c>
       <c r="D18" s="7" t="n">
         <v>1.8</v>
@@ -1284,10 +1284,10 @@
         </is>
       </c>
       <c r="B19" s="7" t="n">
-        <v>28.6</v>
+        <v>28.7</v>
       </c>
       <c r="C19" s="7" t="n">
-        <v>30.4</v>
+        <v>30.5</v>
       </c>
       <c r="D19" s="7" t="n">
         <v>1.8</v>
@@ -1332,10 +1332,10 @@
         </is>
       </c>
       <c r="B20" s="7" t="n">
-        <v>30.4</v>
+        <v>30.5</v>
       </c>
       <c r="C20" s="7" t="n">
-        <v>33.1</v>
+        <v>33.2</v>
       </c>
       <c r="D20" s="7" t="n">
         <v>2.7</v>
@@ -1380,10 +1380,10 @@
         </is>
       </c>
       <c r="B21" s="7" t="n">
-        <v>33.1</v>
+        <v>33.2</v>
       </c>
       <c r="C21" s="7" t="n">
-        <v>34.9</v>
+        <v>35</v>
       </c>
       <c r="D21" s="7" t="n">
         <v>1.8</v>
@@ -1432,10 +1432,10 @@
         </is>
       </c>
       <c r="B22" s="7" t="n">
-        <v>34.9</v>
+        <v>35</v>
       </c>
       <c r="C22" s="7" t="n">
-        <v>36.7</v>
+        <v>36.8</v>
       </c>
       <c r="D22" s="7" t="n">
         <v>1.8</v>
@@ -1480,10 +1480,10 @@
         </is>
       </c>
       <c r="B23" s="7" t="n">
-        <v>36.7</v>
+        <v>36.8</v>
       </c>
       <c r="C23" s="7" t="n">
-        <v>40</v>
+        <v>40.1</v>
       </c>
       <c r="D23" s="7" t="n">
         <v>3.3</v>
@@ -1528,10 +1528,10 @@
         </is>
       </c>
       <c r="B24" s="7" t="n">
-        <v>40</v>
+        <v>40.1</v>
       </c>
       <c r="C24" s="7" t="n">
-        <v>41.8</v>
+        <v>41.9</v>
       </c>
       <c r="D24" s="7" t="n">
         <v>1.8</v>
@@ -1580,10 +1580,10 @@
         </is>
       </c>
       <c r="B25" s="7" t="n">
-        <v>41.8</v>
+        <v>41.9</v>
       </c>
       <c r="C25" s="7" t="n">
-        <v>45.2</v>
+        <v>45.3</v>
       </c>
       <c r="D25" s="7" t="n">
         <v>3.4</v>
@@ -1628,10 +1628,10 @@
         </is>
       </c>
       <c r="B26" s="7" t="n">
-        <v>45.2</v>
+        <v>45.3</v>
       </c>
       <c r="C26" s="7" t="n">
-        <v>47</v>
+        <v>47.1</v>
       </c>
       <c r="D26" s="7" t="n">
         <v>1.8</v>
@@ -1680,10 +1680,10 @@
         </is>
       </c>
       <c r="B27" s="7" t="n">
-        <v>47</v>
+        <v>47.1</v>
       </c>
       <c r="C27" s="7" t="n">
-        <v>48.8</v>
+        <v>48.9</v>
       </c>
       <c r="D27" s="7" t="n">
         <v>1.8</v>
@@ -1728,10 +1728,10 @@
         </is>
       </c>
       <c r="B28" s="7" t="n">
-        <v>48.8</v>
+        <v>48.9</v>
       </c>
       <c r="C28" s="7" t="n">
-        <v>51.9</v>
+        <v>52</v>
       </c>
       <c r="D28" s="7" t="n">
         <v>3.1</v>
@@ -1776,10 +1776,10 @@
         </is>
       </c>
       <c r="B29" s="7" t="n">
-        <v>51.9</v>
+        <v>52</v>
       </c>
       <c r="C29" s="7" t="n">
-        <v>53.8</v>
+        <v>53.9</v>
       </c>
       <c r="D29" s="7" t="n">
         <v>1.9</v>
@@ -1824,10 +1824,10 @@
         </is>
       </c>
       <c r="B30" s="7" t="n">
-        <v>53.8</v>
+        <v>53.9</v>
       </c>
       <c r="C30" s="7" t="n">
-        <v>57.2</v>
+        <v>57.3</v>
       </c>
       <c r="D30" s="7" t="n">
         <v>3.4</v>
@@ -1872,10 +1872,10 @@
         </is>
       </c>
       <c r="B31" s="7" t="n">
-        <v>57.2</v>
+        <v>57.3</v>
       </c>
       <c r="C31" s="7" t="n">
-        <v>60.6</v>
+        <v>60.7</v>
       </c>
       <c r="D31" s="7" t="n">
         <v>3.4</v>
@@ -1920,10 +1920,10 @@
         </is>
       </c>
       <c r="B32" s="7" t="n">
-        <v>60.6</v>
+        <v>60.7</v>
       </c>
       <c r="C32" s="7" t="n">
-        <v>62.7</v>
+        <v>62.8</v>
       </c>
       <c r="D32" s="7" t="n">
         <v>2.1</v>
@@ -1968,10 +1968,10 @@
         </is>
       </c>
       <c r="B33" s="7" t="n">
-        <v>62.7</v>
+        <v>62.8</v>
       </c>
       <c r="C33" s="7" t="n">
-        <v>65.2</v>
+        <v>65.3</v>
       </c>
       <c r="D33" s="7" t="n">
         <v>2.5</v>
@@ -2016,10 +2016,10 @@
         </is>
       </c>
       <c r="B34" s="7" t="n">
-        <v>65.2</v>
+        <v>65.3</v>
       </c>
       <c r="C34" s="7" t="n">
-        <v>67.59999999999999</v>
+        <v>67.7</v>
       </c>
       <c r="D34" s="7" t="n">
         <v>2.4</v>
@@ -2072,10 +2072,10 @@
         </is>
       </c>
       <c r="B35" s="7" t="n">
-        <v>67.59999999999999</v>
+        <v>67.7</v>
       </c>
       <c r="C35" s="7" t="n">
-        <v>70.90000000000001</v>
+        <v>71</v>
       </c>
       <c r="D35" s="7" t="n">
         <v>3.3</v>
@@ -2128,10 +2128,10 @@
         </is>
       </c>
       <c r="B36" s="7" t="n">
-        <v>70.90000000000001</v>
+        <v>71</v>
       </c>
       <c r="C36" s="7" t="n">
-        <v>73.40000000000001</v>
+        <v>73.5</v>
       </c>
       <c r="D36" s="7" t="n">
         <v>2.5</v>
@@ -2184,10 +2184,10 @@
         </is>
       </c>
       <c r="B37" s="7" t="n">
-        <v>73.40000000000001</v>
+        <v>73.5</v>
       </c>
       <c r="C37" s="7" t="n">
-        <v>75.8</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="D37" s="7" t="n">
         <v>2.4</v>
@@ -2465,12 +2465,12 @@
       </c>
       <c r="B3" s="8" t="inlineStr">
         <is>
-          <t>0.7-1.6 秒/镜，3-4 镜快切</t>
+          <t>0.9-1.9 秒/镜，2-3 镜快切</t>
         </is>
       </c>
       <c r="C3" s="8" t="inlineStr">
         <is>
-          <t>这 3 秒决定完播，画面要「炸」，配重音效</t>
+          <t>这 3 秒决定完播，画面要「炸」，配重音效。⚠️别再切碎到 0.8 秒——TTS/真人都会读得发赶，听着假</t>
         </is>
       </c>
     </row>

--- a/workshop/da88ad747a.xlsx
+++ b/workshop/da88ad747a.xlsx
@@ -8,7 +8,7 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="剪辑底稿" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="素材清单（人工去挑）" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="素材采集单（照着办）" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="节奏与声音标准" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
@@ -2249,161 +2249,417 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:I11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="7" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="52" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="30" customWidth="1" min="5" max="5"/>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="5" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="46" customWidth="1" min="6" max="6"/>
+    <col width="30" customWidth="1" min="7" max="7"/>
+    <col width="8" customWidth="1" min="8" max="8"/>
+    <col width="44" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
           <t>序号</t>
         </is>
       </c>
-      <c r="B1" s="4" t="inlineStr">
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>层级</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
         <is>
           <t>场景</t>
         </is>
       </c>
-      <c r="C1" s="4" t="inlineStr">
-        <is>
-          <t>检索词（英文，主用）</t>
-        </is>
-      </c>
-      <c r="D1" s="4" t="inlineStr">
-        <is>
-          <t>建议条数</t>
-        </is>
-      </c>
       <c r="E1" s="4" t="inlineStr">
         <is>
-          <t>来源</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="26" customHeight="1">
-      <c r="A2" s="8" t="inlineStr">
+          <t>覆盖镜次</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>怎么做（检索词 / 拍摄内容）</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>去哪找</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>要几条</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>备注</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="30" customHeight="1">
+      <c r="A2" s="5" t="inlineStr"/>
+      <c r="B2" s="5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B2" s="8" t="inlineStr">
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>L1 自拍</t>
+        </is>
+      </c>
+      <c r="D2" s="6" t="inlineStr">
+        <is>
+          <t>片头钩子 · 自拍空镜</t>
+        </is>
+      </c>
+      <c r="E2" s="5" t="inlineStr">
+        <is>
+          <t>001-002</t>
+        </is>
+      </c>
+      <c r="F2" s="6" t="inlineStr">
+        <is>
+          <t>手机拍：园区大门 / 拉闸门 / 车间过道横移 / 账本红字，每条 5-8 秒</t>
+        </is>
+      </c>
+      <c r="G2" s="6" t="inlineStr">
+        <is>
+          <t>自己拍（手机横屏）</t>
+        </is>
+      </c>
+      <c r="H2" s="5" t="inlineStr">
+        <is>
+          <t>3-4</t>
+        </is>
+      </c>
+      <c r="I2" s="6" t="inlineStr">
+        <is>
+          <t>这 3 秒决定完播。素材站的画面「没有你的厂味」，钩子必用自拍</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="30" customHeight="1">
+      <c r="A3" s="7" t="inlineStr"/>
+      <c r="B3" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C3" s="7" t="inlineStr">
+        <is>
+          <t>L2 免费站</t>
+        </is>
+      </c>
+      <c r="D3" s="8" t="inlineStr">
         <is>
           <t>厂房外景</t>
         </is>
       </c>
-      <c r="C2" s="8" t="inlineStr">
+      <c r="E3" s="7" t="inlineStr">
+        <is>
+          <t>005、009、013、017、021、025、029</t>
+        </is>
+      </c>
+      <c r="F3" s="8" t="inlineStr">
         <is>
           <t>abandoned warehouse / factory closed / shutter door</t>
         </is>
       </c>
-      <c r="D2" s="8" t="inlineStr">
+      <c r="G3" s="8" t="inlineStr">
+        <is>
+          <t>Pexels / Pixabay（免署名、可商用）</t>
+        </is>
+      </c>
+      <c r="H3" s="7" t="inlineStr">
+        <is>
+          <t>3-4</t>
+        </is>
+      </c>
+      <c r="I3" s="8" t="inlineStr">
+        <is>
+          <t>本片复用 7 镜；一次下满，顺着「相似推荐」滚雪球，风格天然统一</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="30" customHeight="1">
+      <c r="A4" s="7" t="inlineStr"/>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>L2 免费站</t>
+        </is>
+      </c>
+      <c r="D4" s="8" t="inlineStr">
+        <is>
+          <t>车间内景</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>006、010、014、018、022、026、030</t>
+        </is>
+      </c>
+      <c r="F4" s="8" t="inlineStr">
+        <is>
+          <t>empty factory / idle production line</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>Pexels / Pixabay（免署名、可商用）</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
+        <is>
+          <t>3-4</t>
+        </is>
+      </c>
+      <c r="I4" s="8" t="inlineStr">
+        <is>
+          <t>本片复用 7 镜；一次下满，顺着「相似推荐」滚雪球，风格天然统一</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="30" customHeight="1">
+      <c r="A5" s="7" t="inlineStr"/>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C5" s="7" t="inlineStr">
+        <is>
+          <t>L2 免费站</t>
+        </is>
+      </c>
+      <c r="D5" s="8" t="inlineStr">
+        <is>
+          <t>仓库</t>
+        </is>
+      </c>
+      <c r="E5" s="7" t="inlineStr">
+        <is>
+          <t>003、007、011、015、019、023、027、031</t>
+        </is>
+      </c>
+      <c r="F5" s="8" t="inlineStr">
+        <is>
+          <t>empty warehouse / cleared shelves</t>
+        </is>
+      </c>
+      <c r="G5" s="8" t="inlineStr">
+        <is>
+          <t>Pexels / Pixabay（免署名、可商用）</t>
+        </is>
+      </c>
+      <c r="H5" s="7" t="inlineStr">
+        <is>
+          <t>3-4</t>
+        </is>
+      </c>
+      <c r="I5" s="8" t="inlineStr">
+        <is>
+          <t>本片复用 8 镜；一次下满，顺着「相似推荐」滚雪球，风格天然统一</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="30" customHeight="1">
+      <c r="A6" s="7" t="inlineStr"/>
+      <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>L2 免费站</t>
+        </is>
+      </c>
+      <c r="D6" s="8" t="inlineStr">
+        <is>
+          <t>货车物流</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>004、008、012、016、020、024、028</t>
+        </is>
+      </c>
+      <c r="F6" s="8" t="inlineStr">
+        <is>
+          <t>empty loading dock / idle truck</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>Pexels / Pixabay（免署名、可商用）</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
+        <is>
+          <t>3-4</t>
+        </is>
+      </c>
+      <c r="I6" s="8" t="inlineStr">
+        <is>
+          <t>本片复用 7 镜；一次下满，顺着「相似推荐」滚雪球，风格天然统一</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="30" customHeight="1">
+      <c r="A7" s="5" t="inlineStr"/>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>L1 自制</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>数据图表 · Excel 出图（叠加层）</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>007、031</t>
+        </is>
+      </c>
+      <c r="F7" s="6" t="inlineStr">
+        <is>
+          <t>用国家统计局 / 地方统计局 / 海关总署的官方数据，自己用 Excel 出图</t>
+        </is>
+      </c>
+      <c r="G7" s="6" t="inlineStr">
+        <is>
+          <t>自己做（Excel 截图或导出 PNG 透明底）</t>
+        </is>
+      </c>
+      <c r="H7" s="5" t="inlineStr">
         <is>
           <t>2-3</t>
         </is>
       </c>
-      <c r="E2" s="8" t="inlineStr">
-        <is>
-          <t>Pexels / Pixabay（免署名可商用）</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="26" customHeight="1">
-      <c r="A3" s="8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B3" s="8" t="inlineStr">
-        <is>
-          <t>车间内景</t>
-        </is>
-      </c>
-      <c r="C3" s="8" t="inlineStr">
-        <is>
-          <t>empty factory / idle production line</t>
-        </is>
-      </c>
-      <c r="D3" s="8" t="inlineStr">
+      <c r="I7" s="6" t="inlineStr">
+        <is>
+          <t>这是叠加在场景素材上的透明图，不占镜次、不替代空镜。带数字的镜头一律上自己出的图——这是可信度来源，也是素材站给不了的</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="30" customHeight="1">
+      <c r="A8" s="5" t="inlineStr"/>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>L1 自拍</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>片尾落点 · 自拍空镜</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>032-033</t>
+        </is>
+      </c>
+      <c r="F8" s="6" t="inlineStr">
+        <is>
+          <t>手机拍：厂区远景 / 关门镜头 / 老板背影 / 空账本合上</t>
+        </is>
+      </c>
+      <c r="G8" s="6" t="inlineStr">
+        <is>
+          <t>自己拍</t>
+        </is>
+      </c>
+      <c r="H8" s="5" t="inlineStr">
         <is>
           <t>2-3</t>
         </is>
       </c>
-      <c r="E3" s="8" t="inlineStr">
-        <is>
-          <t>Pexels / Pixabay（免署名可商用）</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="26" customHeight="1">
-      <c r="A4" s="8" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="B4" s="8" t="inlineStr">
-        <is>
-          <t>仓库</t>
-        </is>
-      </c>
-      <c r="C4" s="8" t="inlineStr">
-        <is>
-          <t>empty warehouse / cleared shelves</t>
-        </is>
-      </c>
-      <c r="D4" s="8" t="inlineStr">
-        <is>
-          <t>2-3</t>
-        </is>
-      </c>
-      <c r="E4" s="8" t="inlineStr">
-        <is>
-          <t>Pexels / Pixabay（免署名可商用）</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="26" customHeight="1">
-      <c r="A5" s="8" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="B5" s="8" t="inlineStr">
-        <is>
-          <t>货车物流</t>
-        </is>
-      </c>
-      <c r="C5" s="8" t="inlineStr">
-        <is>
-          <t>empty loading dock / idle truck</t>
-        </is>
-      </c>
-      <c r="D5" s="8" t="inlineStr">
-        <is>
-          <t>2-3</t>
-        </is>
-      </c>
-      <c r="E5" s="8" t="inlineStr">
-        <is>
-          <t>Pexels / Pixabay（免署名可商用）</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="32" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>Pexels/Pixabay 免署名可商用（注意顶部「赞助」行是 iStock 付费位）；Videvo 逐条协议不同需逐条看；央视/央视频/他人成片一律别用。下载后按「问题类型_场景_序号.mp4」命名，并记入素材台账。</t>
+      <c r="I8" s="6" t="inlineStr">
+        <is>
+          <t>收尾要留白，自拍空镜最压得住；接避坑清单上屏</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="30" customHeight="1">
+      <c r="A9" s="7" t="inlineStr"/>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C9" s="7" t="inlineStr">
+        <is>
+          <t>L3 AI 兜底</t>
+        </is>
+      </c>
+      <c r="D9" s="8" t="inlineStr">
+        <is>
+          <t>仅在实拍和素材站都拿不到时启用</t>
+        </is>
+      </c>
+      <c r="E9" s="7" t="inlineStr"/>
+      <c r="F9" s="8" t="inlineStr">
+        <is>
+          <t>可灵 / 即梦 / Runway；或 Pexels、Pixabay 的 AI 素材专区</t>
+        </is>
+      </c>
+      <c r="G9" s="8" t="inlineStr">
+        <is>
+          <t>按需</t>
+        </is>
+      </c>
+      <c r="H9" s="7" t="inlineStr">
+        <is>
+          <t>0-1</t>
+        </is>
+      </c>
+      <c r="I9" s="8" t="inlineStr">
+        <is>
+          <t>AI 视频细节仍有破绽，一眼假。除非「货堆到天花板」这种实拍拍不到的，否则别用</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="46" customHeight="1">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>用法：从左往右办——『去哪找』决定打开哪个站还是拿手机；办完一行就在「✓」列打个勾。浅蓝底 = 要你自己拍/自己出图（L1），这最容易拖着不做，先办。Pexels/Pixabay 免署名可商用（注意结果顶部「赞助」行是 iStock 付费位）；Videvo 逐条协议不同需逐条看；央视/央视频/他人成片一律别用。下载后按「问题类型_场景_序号.mp4」命名，并记入素材台账（另一张表）。</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A7:E7"/>
+    <mergeCell ref="A11:I11"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/workshop/da88ad747a.xlsx
+++ b/workshop/da88ad747a.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="剪辑底稿" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="素材采集单（照着办）" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="节奏与声音标准" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="剪辑底稿" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="素材清单（人工去挑）" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="节奏与声音标准" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -2249,417 +2249,161 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I11"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="4" customWidth="1" min="1" max="1"/>
-    <col width="5" customWidth="1" min="2" max="2"/>
-    <col width="11" customWidth="1" min="3" max="3"/>
-    <col width="24" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="46" customWidth="1" min="6" max="6"/>
-    <col width="30" customWidth="1" min="7" max="7"/>
-    <col width="8" customWidth="1" min="8" max="8"/>
-    <col width="44" customWidth="1" min="9" max="9"/>
+    <col width="7" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="52" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>序号</t>
         </is>
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>序号</t>
+          <t>场景</t>
         </is>
       </c>
       <c r="C1" s="4" t="inlineStr">
         <is>
-          <t>层级</t>
+          <t>检索词（英文，主用）</t>
         </is>
       </c>
       <c r="D1" s="4" t="inlineStr">
         <is>
-          <t>场景</t>
+          <t>建议条数</t>
         </is>
       </c>
       <c r="E1" s="4" t="inlineStr">
         <is>
-          <t>覆盖镜次</t>
-        </is>
-      </c>
-      <c r="F1" s="4" t="inlineStr">
-        <is>
-          <t>怎么做（检索词 / 拍摄内容）</t>
-        </is>
-      </c>
-      <c r="G1" s="4" t="inlineStr">
-        <is>
-          <t>去哪找</t>
-        </is>
-      </c>
-      <c r="H1" s="4" t="inlineStr">
-        <is>
-          <t>要几条</t>
-        </is>
-      </c>
-      <c r="I1" s="4" t="inlineStr">
-        <is>
-          <t>备注</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="30" customHeight="1">
-      <c r="A2" s="5" t="inlineStr"/>
-      <c r="B2" s="5" t="inlineStr">
+          <t>来源</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="26" customHeight="1">
+      <c r="A2" s="8" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="C2" s="5" t="inlineStr">
-        <is>
-          <t>L1 自拍</t>
-        </is>
-      </c>
-      <c r="D2" s="6" t="inlineStr">
-        <is>
-          <t>片头钩子 · 自拍空镜</t>
-        </is>
-      </c>
-      <c r="E2" s="5" t="inlineStr">
-        <is>
-          <t>001-002</t>
-        </is>
-      </c>
-      <c r="F2" s="6" t="inlineStr">
-        <is>
-          <t>手机拍：园区大门 / 拉闸门 / 车间过道横移 / 账本红字，每条 5-8 秒</t>
-        </is>
-      </c>
-      <c r="G2" s="6" t="inlineStr">
-        <is>
-          <t>自己拍（手机横屏）</t>
-        </is>
-      </c>
-      <c r="H2" s="5" t="inlineStr">
-        <is>
-          <t>3-4</t>
-        </is>
-      </c>
-      <c r="I2" s="6" t="inlineStr">
-        <is>
-          <t>这 3 秒决定完播。素材站的画面「没有你的厂味」，钩子必用自拍</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="30" customHeight="1">
-      <c r="A3" s="7" t="inlineStr"/>
-      <c r="B3" s="7" t="inlineStr">
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>厂房外景</t>
+        </is>
+      </c>
+      <c r="C2" s="8" t="inlineStr">
+        <is>
+          <t>abandoned warehouse / factory closed / shutter door</t>
+        </is>
+      </c>
+      <c r="D2" s="8" t="inlineStr">
+        <is>
+          <t>2-3</t>
+        </is>
+      </c>
+      <c r="E2" s="8" t="inlineStr">
+        <is>
+          <t>Pexels / Pixabay（免署名可商用）</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="26" customHeight="1">
+      <c r="A3" s="8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="C3" s="7" t="inlineStr">
-        <is>
-          <t>L2 免费站</t>
+      <c r="B3" s="8" t="inlineStr">
+        <is>
+          <t>车间内景</t>
+        </is>
+      </c>
+      <c r="C3" s="8" t="inlineStr">
+        <is>
+          <t>empty factory / idle production line</t>
         </is>
       </c>
       <c r="D3" s="8" t="inlineStr">
         <is>
-          <t>厂房外景</t>
-        </is>
-      </c>
-      <c r="E3" s="7" t="inlineStr">
-        <is>
-          <t>005、009、013、017、021、025、029</t>
-        </is>
-      </c>
-      <c r="F3" s="8" t="inlineStr">
-        <is>
-          <t>abandoned warehouse / factory closed / shutter door</t>
-        </is>
-      </c>
-      <c r="G3" s="8" t="inlineStr">
-        <is>
-          <t>Pexels / Pixabay（免署名、可商用）</t>
-        </is>
-      </c>
-      <c r="H3" s="7" t="inlineStr">
-        <is>
-          <t>3-4</t>
-        </is>
-      </c>
-      <c r="I3" s="8" t="inlineStr">
-        <is>
-          <t>本片复用 7 镜；一次下满，顺着「相似推荐」滚雪球，风格天然统一</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="7" t="inlineStr"/>
-      <c r="B4" s="7" t="inlineStr">
+          <t>2-3</t>
+        </is>
+      </c>
+      <c r="E3" s="8" t="inlineStr">
+        <is>
+          <t>Pexels / Pixabay（免署名可商用）</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="26" customHeight="1">
+      <c r="A4" s="8" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="C4" s="7" t="inlineStr">
-        <is>
-          <t>L2 免费站</t>
+      <c r="B4" s="8" t="inlineStr">
+        <is>
+          <t>仓库</t>
+        </is>
+      </c>
+      <c r="C4" s="8" t="inlineStr">
+        <is>
+          <t>empty warehouse / cleared shelves</t>
         </is>
       </c>
       <c r="D4" s="8" t="inlineStr">
         <is>
-          <t>车间内景</t>
-        </is>
-      </c>
-      <c r="E4" s="7" t="inlineStr">
-        <is>
-          <t>006、010、014、018、022、026、030</t>
-        </is>
-      </c>
-      <c r="F4" s="8" t="inlineStr">
-        <is>
-          <t>empty factory / idle production line</t>
-        </is>
-      </c>
-      <c r="G4" s="8" t="inlineStr">
-        <is>
-          <t>Pexels / Pixabay（免署名、可商用）</t>
-        </is>
-      </c>
-      <c r="H4" s="7" t="inlineStr">
-        <is>
-          <t>3-4</t>
-        </is>
-      </c>
-      <c r="I4" s="8" t="inlineStr">
-        <is>
-          <t>本片复用 7 镜；一次下满，顺着「相似推荐」滚雪球，风格天然统一</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="30" customHeight="1">
-      <c r="A5" s="7" t="inlineStr"/>
-      <c r="B5" s="7" t="inlineStr">
+          <t>2-3</t>
+        </is>
+      </c>
+      <c r="E4" s="8" t="inlineStr">
+        <is>
+          <t>Pexels / Pixabay（免署名可商用）</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="26" customHeight="1">
+      <c r="A5" s="8" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="C5" s="7" t="inlineStr">
-        <is>
-          <t>L2 免费站</t>
+      <c r="B5" s="8" t="inlineStr">
+        <is>
+          <t>货车物流</t>
+        </is>
+      </c>
+      <c r="C5" s="8" t="inlineStr">
+        <is>
+          <t>empty loading dock / idle truck</t>
         </is>
       </c>
       <c r="D5" s="8" t="inlineStr">
         <is>
-          <t>仓库</t>
-        </is>
-      </c>
-      <c r="E5" s="7" t="inlineStr">
-        <is>
-          <t>003、007、011、015、019、023、027、031</t>
-        </is>
-      </c>
-      <c r="F5" s="8" t="inlineStr">
-        <is>
-          <t>empty warehouse / cleared shelves</t>
-        </is>
-      </c>
-      <c r="G5" s="8" t="inlineStr">
-        <is>
-          <t>Pexels / Pixabay（免署名、可商用）</t>
-        </is>
-      </c>
-      <c r="H5" s="7" t="inlineStr">
-        <is>
-          <t>3-4</t>
-        </is>
-      </c>
-      <c r="I5" s="8" t="inlineStr">
-        <is>
-          <t>本片复用 8 镜；一次下满，顺着「相似推荐」滚雪球，风格天然统一</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="30" customHeight="1">
-      <c r="A6" s="7" t="inlineStr"/>
-      <c r="B6" s="7" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="C6" s="7" t="inlineStr">
-        <is>
-          <t>L2 免费站</t>
-        </is>
-      </c>
-      <c r="D6" s="8" t="inlineStr">
-        <is>
-          <t>货车物流</t>
-        </is>
-      </c>
-      <c r="E6" s="7" t="inlineStr">
-        <is>
-          <t>004、008、012、016、020、024、028</t>
-        </is>
-      </c>
-      <c r="F6" s="8" t="inlineStr">
-        <is>
-          <t>empty loading dock / idle truck</t>
-        </is>
-      </c>
-      <c r="G6" s="8" t="inlineStr">
-        <is>
-          <t>Pexels / Pixabay（免署名、可商用）</t>
-        </is>
-      </c>
-      <c r="H6" s="7" t="inlineStr">
-        <is>
-          <t>3-4</t>
-        </is>
-      </c>
-      <c r="I6" s="8" t="inlineStr">
-        <is>
-          <t>本片复用 7 镜；一次下满，顺着「相似推荐」滚雪球，风格天然统一</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="30" customHeight="1">
-      <c r="A7" s="5" t="inlineStr"/>
-      <c r="B7" s="5" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="C7" s="5" t="inlineStr">
-        <is>
-          <t>L1 自制</t>
-        </is>
-      </c>
-      <c r="D7" s="6" t="inlineStr">
-        <is>
-          <t>数据图表 · Excel 出图（叠加层）</t>
-        </is>
-      </c>
-      <c r="E7" s="5" t="inlineStr">
-        <is>
-          <t>007、031</t>
-        </is>
-      </c>
-      <c r="F7" s="6" t="inlineStr">
-        <is>
-          <t>用国家统计局 / 地方统计局 / 海关总署的官方数据，自己用 Excel 出图</t>
-        </is>
-      </c>
-      <c r="G7" s="6" t="inlineStr">
-        <is>
-          <t>自己做（Excel 截图或导出 PNG 透明底）</t>
-        </is>
-      </c>
-      <c r="H7" s="5" t="inlineStr">
-        <is>
           <t>2-3</t>
         </is>
       </c>
-      <c r="I7" s="6" t="inlineStr">
-        <is>
-          <t>这是叠加在场景素材上的透明图，不占镜次、不替代空镜。带数字的镜头一律上自己出的图——这是可信度来源，也是素材站给不了的</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="30" customHeight="1">
-      <c r="A8" s="5" t="inlineStr"/>
-      <c r="B8" s="5" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="C8" s="5" t="inlineStr">
-        <is>
-          <t>L1 自拍</t>
-        </is>
-      </c>
-      <c r="D8" s="6" t="inlineStr">
-        <is>
-          <t>片尾落点 · 自拍空镜</t>
-        </is>
-      </c>
-      <c r="E8" s="5" t="inlineStr">
-        <is>
-          <t>032-033</t>
-        </is>
-      </c>
-      <c r="F8" s="6" t="inlineStr">
-        <is>
-          <t>手机拍：厂区远景 / 关门镜头 / 老板背影 / 空账本合上</t>
-        </is>
-      </c>
-      <c r="G8" s="6" t="inlineStr">
-        <is>
-          <t>自己拍</t>
-        </is>
-      </c>
-      <c r="H8" s="5" t="inlineStr">
-        <is>
-          <t>2-3</t>
-        </is>
-      </c>
-      <c r="I8" s="6" t="inlineStr">
-        <is>
-          <t>收尾要留白，自拍空镜最压得住；接避坑清单上屏</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="30" customHeight="1">
-      <c r="A9" s="7" t="inlineStr"/>
-      <c r="B9" s="7" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="C9" s="7" t="inlineStr">
-        <is>
-          <t>L3 AI 兜底</t>
-        </is>
-      </c>
-      <c r="D9" s="8" t="inlineStr">
-        <is>
-          <t>仅在实拍和素材站都拿不到时启用</t>
-        </is>
-      </c>
-      <c r="E9" s="7" t="inlineStr"/>
-      <c r="F9" s="8" t="inlineStr">
-        <is>
-          <t>可灵 / 即梦 / Runway；或 Pexels、Pixabay 的 AI 素材专区</t>
-        </is>
-      </c>
-      <c r="G9" s="8" t="inlineStr">
-        <is>
-          <t>按需</t>
-        </is>
-      </c>
-      <c r="H9" s="7" t="inlineStr">
-        <is>
-          <t>0-1</t>
-        </is>
-      </c>
-      <c r="I9" s="8" t="inlineStr">
-        <is>
-          <t>AI 视频细节仍有破绽，一眼假。除非「货堆到天花板」这种实拍拍不到的，否则别用</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="46" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>用法：从左往右办——『去哪找』决定打开哪个站还是拿手机；办完一行就在「✓」列打个勾。浅蓝底 = 要你自己拍/自己出图（L1），这最容易拖着不做，先办。Pexels/Pixabay 免署名可商用（注意结果顶部「赞助」行是 iStock 付费位）；Videvo 逐条协议不同需逐条看；央视/央视频/他人成片一律别用。下载后按「问题类型_场景_序号.mp4」命名，并记入素材台账（另一张表）。</t>
+      <c r="E5" s="8" t="inlineStr">
+        <is>
+          <t>Pexels / Pixabay（免署名可商用）</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="32" customHeight="1">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>Pexels/Pixabay 免署名可商用（注意顶部「赞助」行是 iStock 付费位）；Videvo 逐条协议不同需逐条看；央视/央视频/他人成片一律别用。下载后按「问题类型_场景_序号.mp4」命名，并记入素材台账。</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A11:I11"/>
+    <mergeCell ref="A7:E7"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/workshop/da88ad747a.xlsx
+++ b/workshop/da88ad747a.xlsx
@@ -8,7 +8,7 @@
   </bookViews>
   <sheets>
     <sheet name="剪辑底稿" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="素材清单（人工去挑）" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="素材采集单（照着办）" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="节奏与声音标准" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
@@ -2249,161 +2249,417 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:I11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="7" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="52" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="30" customWidth="1" min="5" max="5"/>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="5" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="46" customWidth="1" min="6" max="6"/>
+    <col width="30" customWidth="1" min="7" max="7"/>
+    <col width="8" customWidth="1" min="8" max="8"/>
+    <col width="44" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
           <t>序号</t>
         </is>
       </c>
-      <c r="B1" s="4" t="inlineStr">
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>层级</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
         <is>
           <t>场景</t>
         </is>
       </c>
-      <c r="C1" s="4" t="inlineStr">
-        <is>
-          <t>检索词（英文，主用）</t>
-        </is>
-      </c>
-      <c r="D1" s="4" t="inlineStr">
-        <is>
-          <t>建议条数</t>
-        </is>
-      </c>
       <c r="E1" s="4" t="inlineStr">
         <is>
-          <t>来源</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="26" customHeight="1">
-      <c r="A2" s="8" t="inlineStr">
+          <t>覆盖镜次</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>怎么做（检索词 / 拍摄内容）</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>去哪找</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>要几条</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>备注</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="30" customHeight="1">
+      <c r="A2" s="5" t="inlineStr"/>
+      <c r="B2" s="5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B2" s="8" t="inlineStr">
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>L1 自拍</t>
+        </is>
+      </c>
+      <c r="D2" s="6" t="inlineStr">
+        <is>
+          <t>片头钩子 · 自拍空镜</t>
+        </is>
+      </c>
+      <c r="E2" s="5" t="inlineStr">
+        <is>
+          <t>001-002</t>
+        </is>
+      </c>
+      <c r="F2" s="6" t="inlineStr">
+        <is>
+          <t>手机拍：园区大门 / 拉闸门 / 车间过道横移 / 账本红字，每条 5-8 秒</t>
+        </is>
+      </c>
+      <c r="G2" s="6" t="inlineStr">
+        <is>
+          <t>自己拍（手机横屏）</t>
+        </is>
+      </c>
+      <c r="H2" s="5" t="inlineStr">
+        <is>
+          <t>3-4</t>
+        </is>
+      </c>
+      <c r="I2" s="6" t="inlineStr">
+        <is>
+          <t>这 3 秒决定完播。素材站的画面「没有你的厂味」，钩子必用自拍</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="30" customHeight="1">
+      <c r="A3" s="7" t="inlineStr"/>
+      <c r="B3" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C3" s="7" t="inlineStr">
+        <is>
+          <t>L2 免费站</t>
+        </is>
+      </c>
+      <c r="D3" s="8" t="inlineStr">
         <is>
           <t>厂房外景</t>
         </is>
       </c>
-      <c r="C2" s="8" t="inlineStr">
+      <c r="E3" s="7" t="inlineStr">
+        <is>
+          <t>005、009、013、017、021、025、029</t>
+        </is>
+      </c>
+      <c r="F3" s="8" t="inlineStr">
         <is>
           <t>abandoned warehouse / factory closed / shutter door</t>
         </is>
       </c>
-      <c r="D2" s="8" t="inlineStr">
+      <c r="G3" s="8" t="inlineStr">
+        <is>
+          <t>Pexels / Pixabay（免署名、可商用）</t>
+        </is>
+      </c>
+      <c r="H3" s="7" t="inlineStr">
+        <is>
+          <t>3-4</t>
+        </is>
+      </c>
+      <c r="I3" s="8" t="inlineStr">
+        <is>
+          <t>本片复用 7 镜；一次下满，顺着「相似推荐」滚雪球，风格天然统一</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="30" customHeight="1">
+      <c r="A4" s="7" t="inlineStr"/>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>L2 免费站</t>
+        </is>
+      </c>
+      <c r="D4" s="8" t="inlineStr">
+        <is>
+          <t>车间内景</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>006、010、014、018、022、026、030</t>
+        </is>
+      </c>
+      <c r="F4" s="8" t="inlineStr">
+        <is>
+          <t>empty factory / idle production line</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>Pexels / Pixabay（免署名、可商用）</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
+        <is>
+          <t>3-4</t>
+        </is>
+      </c>
+      <c r="I4" s="8" t="inlineStr">
+        <is>
+          <t>本片复用 7 镜；一次下满，顺着「相似推荐」滚雪球，风格天然统一</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="30" customHeight="1">
+      <c r="A5" s="7" t="inlineStr"/>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C5" s="7" t="inlineStr">
+        <is>
+          <t>L2 免费站</t>
+        </is>
+      </c>
+      <c r="D5" s="8" t="inlineStr">
+        <is>
+          <t>仓库</t>
+        </is>
+      </c>
+      <c r="E5" s="7" t="inlineStr">
+        <is>
+          <t>003、007、011、015、019、023、027、031</t>
+        </is>
+      </c>
+      <c r="F5" s="8" t="inlineStr">
+        <is>
+          <t>empty warehouse / cleared shelves</t>
+        </is>
+      </c>
+      <c r="G5" s="8" t="inlineStr">
+        <is>
+          <t>Pexels / Pixabay（免署名、可商用）</t>
+        </is>
+      </c>
+      <c r="H5" s="7" t="inlineStr">
+        <is>
+          <t>3-4</t>
+        </is>
+      </c>
+      <c r="I5" s="8" t="inlineStr">
+        <is>
+          <t>本片复用 8 镜；一次下满，顺着「相似推荐」滚雪球，风格天然统一</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="30" customHeight="1">
+      <c r="A6" s="7" t="inlineStr"/>
+      <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>L2 免费站</t>
+        </is>
+      </c>
+      <c r="D6" s="8" t="inlineStr">
+        <is>
+          <t>货车物流</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>004、008、012、016、020、024、028</t>
+        </is>
+      </c>
+      <c r="F6" s="8" t="inlineStr">
+        <is>
+          <t>empty loading dock / idle truck</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>Pexels / Pixabay（免署名、可商用）</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
+        <is>
+          <t>3-4</t>
+        </is>
+      </c>
+      <c r="I6" s="8" t="inlineStr">
+        <is>
+          <t>本片复用 7 镜；一次下满，顺着「相似推荐」滚雪球，风格天然统一</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="30" customHeight="1">
+      <c r="A7" s="5" t="inlineStr"/>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>L1 自制</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>数据图表 · Excel 出图（叠加层）</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>007、031</t>
+        </is>
+      </c>
+      <c r="F7" s="6" t="inlineStr">
+        <is>
+          <t>用国家统计局 / 地方统计局 / 海关总署的官方数据，自己用 Excel 出图</t>
+        </is>
+      </c>
+      <c r="G7" s="6" t="inlineStr">
+        <is>
+          <t>自己做（Excel 截图或导出 PNG 透明底）</t>
+        </is>
+      </c>
+      <c r="H7" s="5" t="inlineStr">
         <is>
           <t>2-3</t>
         </is>
       </c>
-      <c r="E2" s="8" t="inlineStr">
-        <is>
-          <t>Pexels / Pixabay（免署名可商用）</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="26" customHeight="1">
-      <c r="A3" s="8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B3" s="8" t="inlineStr">
-        <is>
-          <t>车间内景</t>
-        </is>
-      </c>
-      <c r="C3" s="8" t="inlineStr">
-        <is>
-          <t>empty factory / idle production line</t>
-        </is>
-      </c>
-      <c r="D3" s="8" t="inlineStr">
+      <c r="I7" s="6" t="inlineStr">
+        <is>
+          <t>这是叠加在场景素材上的透明图，不占镜次、不替代空镜。带数字的镜头一律上自己出的图——这是可信度来源，也是素材站给不了的</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="30" customHeight="1">
+      <c r="A8" s="5" t="inlineStr"/>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>L1 自拍</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>片尾落点 · 自拍空镜</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>032-033</t>
+        </is>
+      </c>
+      <c r="F8" s="6" t="inlineStr">
+        <is>
+          <t>手机拍：厂区远景 / 关门镜头 / 老板背影 / 空账本合上</t>
+        </is>
+      </c>
+      <c r="G8" s="6" t="inlineStr">
+        <is>
+          <t>自己拍</t>
+        </is>
+      </c>
+      <c r="H8" s="5" t="inlineStr">
         <is>
           <t>2-3</t>
         </is>
       </c>
-      <c r="E3" s="8" t="inlineStr">
-        <is>
-          <t>Pexels / Pixabay（免署名可商用）</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="26" customHeight="1">
-      <c r="A4" s="8" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="B4" s="8" t="inlineStr">
-        <is>
-          <t>仓库</t>
-        </is>
-      </c>
-      <c r="C4" s="8" t="inlineStr">
-        <is>
-          <t>empty warehouse / cleared shelves</t>
-        </is>
-      </c>
-      <c r="D4" s="8" t="inlineStr">
-        <is>
-          <t>2-3</t>
-        </is>
-      </c>
-      <c r="E4" s="8" t="inlineStr">
-        <is>
-          <t>Pexels / Pixabay（免署名可商用）</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="26" customHeight="1">
-      <c r="A5" s="8" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="B5" s="8" t="inlineStr">
-        <is>
-          <t>货车物流</t>
-        </is>
-      </c>
-      <c r="C5" s="8" t="inlineStr">
-        <is>
-          <t>empty loading dock / idle truck</t>
-        </is>
-      </c>
-      <c r="D5" s="8" t="inlineStr">
-        <is>
-          <t>2-3</t>
-        </is>
-      </c>
-      <c r="E5" s="8" t="inlineStr">
-        <is>
-          <t>Pexels / Pixabay（免署名可商用）</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="32" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>Pexels/Pixabay 免署名可商用（注意顶部「赞助」行是 iStock 付费位）；Videvo 逐条协议不同需逐条看；央视/央视频/他人成片一律别用。下载后按「问题类型_场景_序号.mp4」命名，并记入素材台账。</t>
+      <c r="I8" s="6" t="inlineStr">
+        <is>
+          <t>收尾要留白，自拍空镜最压得住；接避坑清单上屏</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="30" customHeight="1">
+      <c r="A9" s="7" t="inlineStr"/>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C9" s="7" t="inlineStr">
+        <is>
+          <t>L3 AI 兜底</t>
+        </is>
+      </c>
+      <c r="D9" s="8" t="inlineStr">
+        <is>
+          <t>仅在实拍和素材站都拿不到时启用</t>
+        </is>
+      </c>
+      <c r="E9" s="7" t="inlineStr"/>
+      <c r="F9" s="8" t="inlineStr">
+        <is>
+          <t>可灵 / 即梦 / Runway；或 Pexels、Pixabay 的 AI 素材专区</t>
+        </is>
+      </c>
+      <c r="G9" s="8" t="inlineStr">
+        <is>
+          <t>按需</t>
+        </is>
+      </c>
+      <c r="H9" s="7" t="inlineStr">
+        <is>
+          <t>0-1</t>
+        </is>
+      </c>
+      <c r="I9" s="8" t="inlineStr">
+        <is>
+          <t>AI 视频细节仍有破绽，一眼假。除非「货堆到天花板」这种实拍拍不到的，否则别用</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="46" customHeight="1">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>用法：从左往右办——『去哪找』决定打开哪个站还是拿手机；办完一行就在「✓」列打个勾。浅蓝底 = 要你自己拍/自己出图（L1），这最容易拖着不做，先办。Pexels/Pixabay 免署名可商用（注意结果顶部「赞助」行是 iStock 付费位）；Videvo 逐条协议不同需逐条看；央视/央视频/他人成片一律别用。下载后按「问题类型_场景_序号.mp4」命名，并记入素材台账（另一张表）。</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A7:E7"/>
+    <mergeCell ref="A11:I11"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/workshop/da88ad747a.xlsx
+++ b/workshop/da88ad747a.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="剪辑底稿" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="素材采集单（照着办）" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="节奏与声音标准" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="剪辑底稿" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="素材采集单（照着办）" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="节奏与声音标准" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -485,7 +485,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L37"/>
+  <dimension ref="A1:L34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -512,7 +512,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>问题类型：倒闭 / 关停　地区：江苏　内容价值：★92.5　总时长：75.9 秒　镜次：33</t>
+          <t>问题类型：倒闭 / 关停　地区：江苏　内容价值：★92.5　总时长：70.6 秒　镜次：30</t>
         </is>
       </c>
     </row>
@@ -747,14 +747,14 @@
         <v>4</v>
       </c>
       <c r="C8" s="7" t="n">
-        <v>5.5</v>
+        <v>6.5</v>
       </c>
       <c r="D8" s="7" t="n">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="E8" s="8" t="inlineStr">
         <is>
-          <t>症结在订单依赖</t>
+          <t>栽在「倒闭 / 关停」上</t>
         </is>
       </c>
       <c r="F8" s="7" t="inlineStr">
@@ -792,27 +792,27 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>5.5</v>
+        <v>6.5</v>
       </c>
       <c r="C9" s="7" t="n">
         <v>8.1</v>
       </c>
       <c r="D9" s="7" t="n">
-        <v>2.6</v>
+        <v>1.6</v>
       </c>
       <c r="E9" s="8" t="inlineStr">
         <is>
-          <t>账期拉长，成本上升三头一起压</t>
+          <t>先把事实摆出来</t>
         </is>
       </c>
       <c r="F9" s="7" t="inlineStr">
         <is>
-          <t>推进</t>
+          <t>陈述/数字重音</t>
         </is>
       </c>
       <c r="G9" s="7" t="inlineStr">
         <is>
-          <t>空镜</t>
+          <t>图表+实拍</t>
         </is>
       </c>
       <c r="H9" s="8" t="inlineStr">
@@ -824,12 +824,12 @@
       <c r="J9" s="7" t="inlineStr"/>
       <c r="K9" s="7" t="inlineStr">
         <is>
-          <t>开场悬念</t>
+          <t>中段推进</t>
         </is>
       </c>
       <c r="L9" s="7" t="inlineStr">
         <is>
-          <t>叠化</t>
+          <t>硬切</t>
         </is>
       </c>
     </row>
@@ -843,14 +843,14 @@
         <v>8.1</v>
       </c>
       <c r="C10" s="7" t="n">
-        <v>9.699999999999999</v>
+        <v>11</v>
       </c>
       <c r="D10" s="7" t="n">
-        <v>1.6</v>
+        <v>2.9</v>
       </c>
       <c r="E10" s="8" t="inlineStr">
         <is>
-          <t>先把事实说清楚</t>
+          <t>常州小微五金代工厂5年即破产</t>
         </is>
       </c>
       <c r="F10" s="7" t="inlineStr">
@@ -868,8 +868,16 @@
           <t>【待挑】倒闭关停_车间内景_006　搜：empty factory / idle production line</t>
         </is>
       </c>
-      <c r="I10" s="8" t="inlineStr"/>
-      <c r="J10" s="7" t="inlineStr"/>
+      <c r="I10" s="8" t="inlineStr">
+        <is>
+          <t>数字上大字幕：5年</t>
+        </is>
+      </c>
+      <c r="J10" s="7" t="inlineStr">
+        <is>
+          <t>数字叮</t>
+        </is>
+      </c>
       <c r="K10" s="7" t="inlineStr">
         <is>
           <t>中段推进</t>
@@ -888,17 +896,17 @@
         </is>
       </c>
       <c r="B11" s="7" t="n">
-        <v>9.699999999999999</v>
+        <v>11</v>
       </c>
       <c r="C11" s="7" t="n">
-        <v>12.6</v>
+        <v>14.4</v>
       </c>
       <c r="D11" s="7" t="n">
-        <v>2.9</v>
+        <v>3.4</v>
       </c>
       <c r="E11" s="8" t="inlineStr">
         <is>
-          <t>常州小微五金代工厂5年即破产</t>
+          <t>抗风险弱，订单依赖+账期延长+成本上升</t>
         </is>
       </c>
       <c r="F11" s="7" t="inlineStr">
@@ -916,16 +924,8 @@
           <t>【待挑】倒闭关停_仓库_007　搜：empty warehouse / cleared shelves</t>
         </is>
       </c>
-      <c r="I11" s="8" t="inlineStr">
-        <is>
-          <t>数字上大字幕：5年</t>
-        </is>
-      </c>
-      <c r="J11" s="7" t="inlineStr">
-        <is>
-          <t>数字叮</t>
-        </is>
-      </c>
+      <c r="I11" s="8" t="inlineStr"/>
+      <c r="J11" s="7" t="inlineStr"/>
       <c r="K11" s="7" t="inlineStr">
         <is>
           <t>中段推进</t>
@@ -944,17 +944,17 @@
         </is>
       </c>
       <c r="B12" s="7" t="n">
-        <v>12.6</v>
+        <v>14.4</v>
       </c>
       <c r="C12" s="7" t="n">
-        <v>16</v>
+        <v>17.3</v>
       </c>
       <c r="D12" s="7" t="n">
-        <v>3.4</v>
+        <v>2.9</v>
       </c>
       <c r="E12" s="8" t="inlineStr">
         <is>
-          <t>抗风险弱，订单依赖+账期延长+成本上升</t>
+          <t>管理短板在市场调整期集中暴露</t>
         </is>
       </c>
       <c r="F12" s="7" t="inlineStr">
@@ -992,27 +992,27 @@
         </is>
       </c>
       <c r="B13" s="7" t="n">
-        <v>16</v>
+        <v>17.3</v>
       </c>
       <c r="C13" s="7" t="n">
-        <v>18.9</v>
+        <v>19.1</v>
       </c>
       <c r="D13" s="7" t="n">
-        <v>2.9</v>
+        <v>1.8</v>
       </c>
       <c r="E13" s="8" t="inlineStr">
         <is>
-          <t>管理短板在市场调整期集中暴露</t>
+          <t>打个比方</t>
         </is>
       </c>
       <c r="F13" s="7" t="inlineStr">
         <is>
-          <t>陈述/数字重音</t>
+          <t>转折/停顿</t>
         </is>
       </c>
       <c r="G13" s="7" t="inlineStr">
         <is>
-          <t>图表+实拍</t>
+          <t>素材(比喻画面)</t>
         </is>
       </c>
       <c r="H13" s="8" t="inlineStr">
@@ -1040,17 +1040,17 @@
         </is>
       </c>
       <c r="B14" s="7" t="n">
-        <v>18.9</v>
+        <v>19.1</v>
       </c>
       <c r="C14" s="7" t="n">
-        <v>20.7</v>
+        <v>20.9</v>
       </c>
       <c r="D14" s="7" t="n">
         <v>1.8</v>
       </c>
       <c r="E14" s="8" t="inlineStr">
         <is>
-          <t>打个比方</t>
+          <t>厂子就是一口锅</t>
         </is>
       </c>
       <c r="F14" s="7" t="inlineStr">
@@ -1088,17 +1088,17 @@
         </is>
       </c>
       <c r="B15" s="7" t="n">
-        <v>20.7</v>
+        <v>20.9</v>
       </c>
       <c r="C15" s="7" t="n">
-        <v>22.5</v>
+        <v>23.4</v>
       </c>
       <c r="D15" s="7" t="n">
-        <v>1.8</v>
+        <v>2.5</v>
       </c>
       <c r="E15" s="8" t="inlineStr">
         <is>
-          <t>厂子就是一口锅</t>
+          <t>订单是火，现金是锅里的水</t>
         </is>
       </c>
       <c r="F15" s="7" t="inlineStr">
@@ -1136,17 +1136,17 @@
         </is>
       </c>
       <c r="B16" s="7" t="n">
-        <v>22.5</v>
+        <v>23.4</v>
       </c>
       <c r="C16" s="7" t="n">
-        <v>25</v>
+        <v>25.3</v>
       </c>
       <c r="D16" s="7" t="n">
-        <v>2.5</v>
+        <v>1.9</v>
       </c>
       <c r="E16" s="8" t="inlineStr">
         <is>
-          <t>订单是火，现金是锅里的水</t>
+          <t>火一停，水凉得飞快</t>
         </is>
       </c>
       <c r="F16" s="7" t="inlineStr">
@@ -1184,27 +1184,27 @@
         </is>
       </c>
       <c r="B17" s="7" t="n">
-        <v>25</v>
+        <v>25.3</v>
       </c>
       <c r="C17" s="7" t="n">
-        <v>26.9</v>
+        <v>27.4</v>
       </c>
       <c r="D17" s="7" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="E17" s="8" t="inlineStr">
         <is>
-          <t>火一停，水凉得飞快</t>
+          <t>本案的财务病灶很具体</t>
         </is>
       </c>
       <c r="F17" s="7" t="inlineStr">
         <is>
-          <t>转折/停顿</t>
+          <t>逐条拆解</t>
         </is>
       </c>
       <c r="G17" s="7" t="inlineStr">
         <is>
-          <t>素材(比喻画面)</t>
+          <t>图表+文字卡</t>
         </is>
       </c>
       <c r="H17" s="8" t="inlineStr">
@@ -1232,17 +1232,17 @@
         </is>
       </c>
       <c r="B18" s="7" t="n">
-        <v>26.9</v>
+        <v>27.4</v>
       </c>
       <c r="C18" s="7" t="n">
-        <v>28.7</v>
+        <v>29.3</v>
       </c>
       <c r="D18" s="7" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="E18" s="8" t="inlineStr">
         <is>
-          <t>①战略视角</t>
+          <t>订单高度依赖大客户</t>
         </is>
       </c>
       <c r="F18" s="7" t="inlineStr">
@@ -1260,11 +1260,7 @@
           <t>【待挑】倒闭关停_车间内景_014　搜：empty factory / idle production line</t>
         </is>
       </c>
-      <c r="I18" s="8" t="inlineStr">
-        <is>
-          <t>视角卡：战略视角</t>
-        </is>
-      </c>
+      <c r="I18" s="8" t="inlineStr"/>
       <c r="J18" s="7" t="inlineStr"/>
       <c r="K18" s="7" t="inlineStr">
         <is>
@@ -1284,17 +1280,17 @@
         </is>
       </c>
       <c r="B19" s="7" t="n">
-        <v>28.7</v>
+        <v>29.3</v>
       </c>
       <c r="C19" s="7" t="n">
-        <v>30.5</v>
+        <v>31.8</v>
       </c>
       <c r="D19" s="7" t="n">
-        <v>1.8</v>
+        <v>2.5</v>
       </c>
       <c r="E19" s="8" t="inlineStr">
         <is>
-          <t>是否死守低端红海</t>
+          <t>账期被拉长，成本刚性上升</t>
         </is>
       </c>
       <c r="F19" s="7" t="inlineStr">
@@ -1332,17 +1328,17 @@
         </is>
       </c>
       <c r="B20" s="7" t="n">
-        <v>30.5</v>
+        <v>31.8</v>
       </c>
       <c r="C20" s="7" t="n">
-        <v>33.2</v>
+        <v>33.6</v>
       </c>
       <c r="D20" s="7" t="n">
-        <v>2.7</v>
+        <v>1.8</v>
       </c>
       <c r="E20" s="8" t="inlineStr">
         <is>
-          <t>无产品壁垒，靠低价内卷抢单</t>
+          <t>毛利被两头夹</t>
         </is>
       </c>
       <c r="F20" s="7" t="inlineStr">
@@ -1380,17 +1376,17 @@
         </is>
       </c>
       <c r="B21" s="7" t="n">
-        <v>33.2</v>
+        <v>33.6</v>
       </c>
       <c r="C21" s="7" t="n">
-        <v>35</v>
+        <v>36.3</v>
       </c>
       <c r="D21" s="7" t="n">
-        <v>1.8</v>
+        <v>2.7</v>
       </c>
       <c r="E21" s="8" t="inlineStr">
         <is>
-          <t>②财务视角</t>
+          <t>把这家五金机械厂的账拆开看</t>
         </is>
       </c>
       <c r="F21" s="7" t="inlineStr">
@@ -1408,11 +1404,7 @@
           <t>【待挑】倒闭关停_厂房外景_017　搜：abandoned warehouse / factory closed / shutter door</t>
         </is>
       </c>
-      <c r="I21" s="8" t="inlineStr">
-        <is>
-          <t>视角卡：财务视角</t>
-        </is>
-      </c>
+      <c r="I21" s="8" t="inlineStr"/>
       <c r="J21" s="7" t="inlineStr"/>
       <c r="K21" s="7" t="inlineStr">
         <is>
@@ -1432,17 +1424,17 @@
         </is>
       </c>
       <c r="B22" s="7" t="n">
-        <v>35</v>
+        <v>36.3</v>
       </c>
       <c r="C22" s="7" t="n">
-        <v>36.8</v>
+        <v>39.7</v>
       </c>
       <c r="D22" s="7" t="n">
-        <v>1.8</v>
+        <v>3.4</v>
       </c>
       <c r="E22" s="8" t="inlineStr">
         <is>
-          <t>现金流是否断裂</t>
+          <t>倒闭极少突发，是现金循环周期被拉长</t>
         </is>
       </c>
       <c r="F22" s="7" t="inlineStr">
@@ -1480,17 +1472,17 @@
         </is>
       </c>
       <c r="B23" s="7" t="n">
-        <v>36.8</v>
+        <v>39.7</v>
       </c>
       <c r="C23" s="7" t="n">
-        <v>40.1</v>
+        <v>41.8</v>
       </c>
       <c r="D23" s="7" t="n">
-        <v>3.3</v>
+        <v>2.1</v>
       </c>
       <c r="E23" s="8" t="inlineStr">
         <is>
-          <t>应收账款/账期是否被大客户拉长抽</t>
+          <t>应收收不回，存货压钱</t>
         </is>
       </c>
       <c r="F23" s="7" t="inlineStr">
@@ -1528,17 +1520,17 @@
         </is>
       </c>
       <c r="B24" s="7" t="n">
-        <v>40.1</v>
+        <v>41.8</v>
       </c>
       <c r="C24" s="7" t="n">
-        <v>41.9</v>
+        <v>44.5</v>
       </c>
       <c r="D24" s="7" t="n">
-        <v>1.8</v>
+        <v>2.7</v>
       </c>
       <c r="E24" s="8" t="inlineStr">
         <is>
-          <t>③运营视角</t>
+          <t>扩产吞现金，三条管道同时漏</t>
         </is>
       </c>
       <c r="F24" s="7" t="inlineStr">
@@ -1556,11 +1548,7 @@
           <t>【待挑】倒闭关停_货车物流_020　搜：empty loading dock / idle truck</t>
         </is>
       </c>
-      <c r="I24" s="8" t="inlineStr">
-        <is>
-          <t>视角卡：运营视角</t>
-        </is>
-      </c>
+      <c r="I24" s="8" t="inlineStr"/>
       <c r="J24" s="7" t="inlineStr"/>
       <c r="K24" s="7" t="inlineStr">
         <is>
@@ -1580,17 +1568,17 @@
         </is>
       </c>
       <c r="B25" s="7" t="n">
-        <v>41.9</v>
+        <v>44.5</v>
       </c>
       <c r="C25" s="7" t="n">
-        <v>45.3</v>
+        <v>46.6</v>
       </c>
       <c r="D25" s="7" t="n">
-        <v>3.4</v>
+        <v>2.1</v>
       </c>
       <c r="E25" s="8" t="inlineStr">
         <is>
-          <t>成本结构是否失衡（原料涨，终端不涨，增收不增利）</t>
+          <t>安全垫撑不到回款那天</t>
         </is>
       </c>
       <c r="F25" s="7" t="inlineStr">
@@ -1628,17 +1616,17 @@
         </is>
       </c>
       <c r="B26" s="7" t="n">
-        <v>45.3</v>
+        <v>46.6</v>
       </c>
       <c r="C26" s="7" t="n">
-        <v>47.1</v>
+        <v>48.5</v>
       </c>
       <c r="D26" s="7" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="E26" s="8" t="inlineStr">
         <is>
-          <t>④心智视角</t>
+          <t>看三数，安全垫月数</t>
         </is>
       </c>
       <c r="F26" s="7" t="inlineStr">
@@ -1656,11 +1644,7 @@
           <t>【待挑】倒闭关停_车间内景_022　搜：empty factory / idle production line</t>
         </is>
       </c>
-      <c r="I26" s="8" t="inlineStr">
-        <is>
-          <t>视角卡：心智视角</t>
-        </is>
-      </c>
+      <c r="I26" s="8" t="inlineStr"/>
       <c r="J26" s="7" t="inlineStr"/>
       <c r="K26" s="7" t="inlineStr">
         <is>
@@ -1680,17 +1664,17 @@
         </is>
       </c>
       <c r="B27" s="7" t="n">
-        <v>47.1</v>
+        <v>48.5</v>
       </c>
       <c r="C27" s="7" t="n">
-        <v>48.9</v>
+        <v>51</v>
       </c>
       <c r="D27" s="7" t="n">
-        <v>1.8</v>
+        <v>2.5</v>
       </c>
       <c r="E27" s="8" t="inlineStr">
         <is>
-          <t>老板是否路径依赖</t>
+          <t>应收周转天数，资产负债率</t>
         </is>
       </c>
       <c r="F27" s="7" t="inlineStr">
@@ -1728,27 +1712,27 @@
         </is>
       </c>
       <c r="B28" s="7" t="n">
-        <v>48.9</v>
+        <v>51</v>
       </c>
       <c r="C28" s="7" t="n">
-        <v>52</v>
+        <v>53.1</v>
       </c>
       <c r="D28" s="7" t="n">
-        <v>3.1</v>
+        <v>2.1</v>
       </c>
       <c r="E28" s="8" t="inlineStr">
         <is>
-          <t>不愿技改升级，把困境归咎大环境</t>
+          <t>关门不是哪一天的决定</t>
         </is>
       </c>
       <c r="F28" s="7" t="inlineStr">
         <is>
-          <t>逐条拆解</t>
+          <t>转折/停顿</t>
         </is>
       </c>
       <c r="G28" s="7" t="inlineStr">
         <is>
-          <t>图表+文字卡</t>
+          <t>素材(比喻画面)</t>
         </is>
       </c>
       <c r="H28" s="8" t="inlineStr">
@@ -1776,27 +1760,27 @@
         </is>
       </c>
       <c r="B29" s="7" t="n">
-        <v>52</v>
+        <v>53.1</v>
       </c>
       <c r="C29" s="7" t="n">
-        <v>53.9</v>
+        <v>55.6</v>
       </c>
       <c r="D29" s="7" t="n">
-        <v>1.9</v>
+        <v>2.5</v>
       </c>
       <c r="E29" s="8" t="inlineStr">
         <is>
-          <t>公开信息点名的问题</t>
+          <t>是每一次「再撑撑」的累加</t>
         </is>
       </c>
       <c r="F29" s="7" t="inlineStr">
         <is>
-          <t>逐条拆解</t>
+          <t>转折/停顿</t>
         </is>
       </c>
       <c r="G29" s="7" t="inlineStr">
         <is>
-          <t>图表+文字卡</t>
+          <t>素材(比喻画面)</t>
         </is>
       </c>
       <c r="H29" s="8" t="inlineStr">
@@ -1824,27 +1808,27 @@
         </is>
       </c>
       <c r="B30" s="7" t="n">
-        <v>53.9</v>
+        <v>55.6</v>
       </c>
       <c r="C30" s="7" t="n">
-        <v>57.3</v>
+        <v>59.1</v>
       </c>
       <c r="D30" s="7" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="E30" s="8" t="inlineStr">
         <is>
-          <t>小微代工厂高度依赖订单稳定性与客户回款</t>
+          <t>记住一句话，潮水退了才知道谁没穿裤</t>
         </is>
       </c>
       <c r="F30" s="7" t="inlineStr">
         <is>
-          <t>逐条拆解</t>
+          <t>落点/留白</t>
         </is>
       </c>
       <c r="G30" s="7" t="inlineStr">
         <is>
-          <t>图表+文字卡</t>
+          <t>实拍+文字卡</t>
         </is>
       </c>
       <c r="H30" s="8" t="inlineStr">
@@ -1852,16 +1836,24 @@
           <t>【待挑】倒闭关停_车间内景_026　搜：empty factory / idle production line</t>
         </is>
       </c>
-      <c r="I30" s="8" t="inlineStr"/>
-      <c r="J30" s="7" t="inlineStr"/>
+      <c r="I30" s="8" t="inlineStr">
+        <is>
+          <t>避坑清单上屏（≤3 条）</t>
+        </is>
+      </c>
+      <c r="J30" s="7" t="inlineStr">
+        <is>
+          <t>结论咚</t>
+        </is>
+      </c>
       <c r="K30" s="7" t="inlineStr">
         <is>
-          <t>中段推进</t>
+          <t>结尾收束</t>
         </is>
       </c>
       <c r="L30" s="7" t="inlineStr">
         <is>
-          <t>硬切</t>
+          <t>叠化</t>
         </is>
       </c>
     </row>
@@ -1872,27 +1864,27 @@
         </is>
       </c>
       <c r="B31" s="7" t="n">
-        <v>57.3</v>
+        <v>59.1</v>
       </c>
       <c r="C31" s="7" t="n">
-        <v>60.7</v>
+        <v>61.5</v>
       </c>
       <c r="D31" s="7" t="n">
-        <v>3.4</v>
+        <v>2.4</v>
       </c>
       <c r="E31" s="8" t="inlineStr">
         <is>
-          <t>外部需求下滑，订单被压价，账期延长</t>
+          <t>安全垫比规模重要</t>
         </is>
       </c>
       <c r="F31" s="7" t="inlineStr">
         <is>
-          <t>逐条拆解</t>
+          <t>落点/留白</t>
         </is>
       </c>
       <c r="G31" s="7" t="inlineStr">
         <is>
-          <t>图表+文字卡</t>
+          <t>实拍+文字卡</t>
         </is>
       </c>
       <c r="H31" s="8" t="inlineStr">
@@ -1900,16 +1892,24 @@
           <t>【待挑】倒闭关停_仓库_027　搜：empty warehouse / cleared shelves</t>
         </is>
       </c>
-      <c r="I31" s="8" t="inlineStr"/>
-      <c r="J31" s="7" t="inlineStr"/>
+      <c r="I31" s="8" t="inlineStr">
+        <is>
+          <t>避坑清单上屏（≤3 条）</t>
+        </is>
+      </c>
+      <c r="J31" s="7" t="inlineStr">
+        <is>
+          <t>结论咚</t>
+        </is>
+      </c>
       <c r="K31" s="7" t="inlineStr">
         <is>
-          <t>中段推进</t>
+          <t>结尾收束</t>
         </is>
       </c>
       <c r="L31" s="7" t="inlineStr">
         <is>
-          <t>硬切</t>
+          <t>叠化</t>
         </is>
       </c>
     </row>
@@ -1920,27 +1920,27 @@
         </is>
       </c>
       <c r="B32" s="7" t="n">
-        <v>60.7</v>
+        <v>61.5</v>
       </c>
       <c r="C32" s="7" t="n">
-        <v>62.8</v>
+        <v>65.7</v>
       </c>
       <c r="D32" s="7" t="n">
-        <v>2.1</v>
+        <v>4.2</v>
       </c>
       <c r="E32" s="8" t="inlineStr">
         <is>
-          <t>关门不是哪一天的决定</t>
+          <t>同类厂记住三件事，①留足 6 个月现金安全垫再扩张</t>
         </is>
       </c>
       <c r="F32" s="7" t="inlineStr">
         <is>
-          <t>转折/停顿</t>
+          <t>落点/留白</t>
         </is>
       </c>
       <c r="G32" s="7" t="inlineStr">
         <is>
-          <t>素材(比喻画面)</t>
+          <t>实拍+文字卡</t>
         </is>
       </c>
       <c r="H32" s="8" t="inlineStr">
@@ -1948,16 +1948,24 @@
           <t>【待挑】倒闭关停_货车物流_028　搜：empty loading dock / idle truck</t>
         </is>
       </c>
-      <c r="I32" s="8" t="inlineStr"/>
-      <c r="J32" s="7" t="inlineStr"/>
+      <c r="I32" s="8" t="inlineStr">
+        <is>
+          <t>数字上大字幕：6 个月</t>
+        </is>
+      </c>
+      <c r="J32" s="7" t="inlineStr">
+        <is>
+          <t>数字叮</t>
+        </is>
+      </c>
       <c r="K32" s="7" t="inlineStr">
         <is>
-          <t>中段推进</t>
+          <t>结尾收束</t>
         </is>
       </c>
       <c r="L32" s="7" t="inlineStr">
         <is>
-          <t>硬切</t>
+          <t>叠化</t>
         </is>
       </c>
     </row>
@@ -1968,27 +1976,27 @@
         </is>
       </c>
       <c r="B33" s="7" t="n">
-        <v>62.8</v>
+        <v>65.7</v>
       </c>
       <c r="C33" s="7" t="n">
-        <v>65.3</v>
+        <v>68.2</v>
       </c>
       <c r="D33" s="7" t="n">
         <v>2.5</v>
       </c>
       <c r="E33" s="8" t="inlineStr">
         <is>
-          <t>是每一次「再撑撑」的累加</t>
+          <t>②砍掉不赚钱的低端红海单</t>
         </is>
       </c>
       <c r="F33" s="7" t="inlineStr">
         <is>
-          <t>转折/停顿</t>
+          <t>落点/留白</t>
         </is>
       </c>
       <c r="G33" s="7" t="inlineStr">
         <is>
-          <t>素材(比喻画面)</t>
+          <t>实拍+文字卡</t>
         </is>
       </c>
       <c r="H33" s="8" t="inlineStr">
@@ -1996,16 +2004,24 @@
           <t>【待挑】倒闭关停_厂房外景_029　搜：abandoned warehouse / factory closed / shutter door</t>
         </is>
       </c>
-      <c r="I33" s="8" t="inlineStr"/>
-      <c r="J33" s="7" t="inlineStr"/>
+      <c r="I33" s="8" t="inlineStr">
+        <is>
+          <t>避坑清单上屏（≤3 条）</t>
+        </is>
+      </c>
+      <c r="J33" s="7" t="inlineStr">
+        <is>
+          <t>结论咚</t>
+        </is>
+      </c>
       <c r="K33" s="7" t="inlineStr">
         <is>
-          <t>中段推进</t>
+          <t>结尾收束</t>
         </is>
       </c>
       <c r="L33" s="7" t="inlineStr">
         <is>
-          <t>硬切</t>
+          <t>叠化</t>
         </is>
       </c>
     </row>
@@ -2016,17 +2032,17 @@
         </is>
       </c>
       <c r="B34" s="7" t="n">
-        <v>65.3</v>
+        <v>68.2</v>
       </c>
       <c r="C34" s="7" t="n">
-        <v>67.7</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="D34" s="7" t="n">
         <v>2.4</v>
       </c>
       <c r="E34" s="8" t="inlineStr">
         <is>
-          <t>最后给同类厂三句话</t>
+          <t>③每年固定比例投技改</t>
         </is>
       </c>
       <c r="F34" s="7" t="inlineStr">
@@ -2060,174 +2076,6 @@
         </is>
       </c>
       <c r="L34" s="7" t="inlineStr">
-        <is>
-          <t>叠化</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="30" customHeight="1">
-      <c r="A35" s="7" t="inlineStr">
-        <is>
-          <t>031</t>
-        </is>
-      </c>
-      <c r="B35" s="7" t="n">
-        <v>67.7</v>
-      </c>
-      <c r="C35" s="7" t="n">
-        <v>71</v>
-      </c>
-      <c r="D35" s="7" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="E35" s="8" t="inlineStr">
-        <is>
-          <t>①留足 6 个月现金安全垫再扩张</t>
-        </is>
-      </c>
-      <c r="F35" s="7" t="inlineStr">
-        <is>
-          <t>落点/留白</t>
-        </is>
-      </c>
-      <c r="G35" s="7" t="inlineStr">
-        <is>
-          <t>实拍+文字卡</t>
-        </is>
-      </c>
-      <c r="H35" s="8" t="inlineStr">
-        <is>
-          <t>【待挑】倒闭关停_仓库_031　搜：empty warehouse / cleared shelves</t>
-        </is>
-      </c>
-      <c r="I35" s="8" t="inlineStr">
-        <is>
-          <t>数字上大字幕：6 个月</t>
-        </is>
-      </c>
-      <c r="J35" s="7" t="inlineStr">
-        <is>
-          <t>数字叮</t>
-        </is>
-      </c>
-      <c r="K35" s="7" t="inlineStr">
-        <is>
-          <t>结尾收束</t>
-        </is>
-      </c>
-      <c r="L35" s="7" t="inlineStr">
-        <is>
-          <t>叠化</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="30" customHeight="1">
-      <c r="A36" s="7" t="inlineStr">
-        <is>
-          <t>032</t>
-        </is>
-      </c>
-      <c r="B36" s="7" t="n">
-        <v>71</v>
-      </c>
-      <c r="C36" s="7" t="n">
-        <v>73.5</v>
-      </c>
-      <c r="D36" s="7" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="E36" s="8" t="inlineStr">
-        <is>
-          <t>②砍掉不赚钱的低端红海单</t>
-        </is>
-      </c>
-      <c r="F36" s="7" t="inlineStr">
-        <is>
-          <t>落点/留白</t>
-        </is>
-      </c>
-      <c r="G36" s="7" t="inlineStr">
-        <is>
-          <t>实拍+文字卡</t>
-        </is>
-      </c>
-      <c r="H36" s="8" t="inlineStr">
-        <is>
-          <t>【待挑】倒闭关停_货车物流_032　搜：empty loading dock / idle truck</t>
-        </is>
-      </c>
-      <c r="I36" s="8" t="inlineStr">
-        <is>
-          <t>避坑清单上屏（≤3 条）</t>
-        </is>
-      </c>
-      <c r="J36" s="7" t="inlineStr">
-        <is>
-          <t>结论咚</t>
-        </is>
-      </c>
-      <c r="K36" s="7" t="inlineStr">
-        <is>
-          <t>结尾收束</t>
-        </is>
-      </c>
-      <c r="L36" s="7" t="inlineStr">
-        <is>
-          <t>叠化</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="30" customHeight="1">
-      <c r="A37" s="7" t="inlineStr">
-        <is>
-          <t>033</t>
-        </is>
-      </c>
-      <c r="B37" s="7" t="n">
-        <v>73.5</v>
-      </c>
-      <c r="C37" s="7" t="n">
-        <v>75.90000000000001</v>
-      </c>
-      <c r="D37" s="7" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="E37" s="8" t="inlineStr">
-        <is>
-          <t>③每年固定比例投技改</t>
-        </is>
-      </c>
-      <c r="F37" s="7" t="inlineStr">
-        <is>
-          <t>落点/留白</t>
-        </is>
-      </c>
-      <c r="G37" s="7" t="inlineStr">
-        <is>
-          <t>实拍+文字卡</t>
-        </is>
-      </c>
-      <c r="H37" s="8" t="inlineStr">
-        <is>
-          <t>【待挑】倒闭关停_厂房外景_033　搜：abandoned warehouse / factory closed / shutter door</t>
-        </is>
-      </c>
-      <c r="I37" s="8" t="inlineStr">
-        <is>
-          <t>避坑清单上屏（≤3 条）</t>
-        </is>
-      </c>
-      <c r="J37" s="7" t="inlineStr">
-        <is>
-          <t>结论咚</t>
-        </is>
-      </c>
-      <c r="K37" s="7" t="inlineStr">
-        <is>
-          <t>结尾收束</t>
-        </is>
-      </c>
-      <c r="L37" s="7" t="inlineStr">
         <is>
           <t>叠化</t>
         </is>
@@ -2372,7 +2220,7 @@
       </c>
       <c r="E3" s="7" t="inlineStr">
         <is>
-          <t>005、009、013、017、021、025、029</t>
+          <t>005、009、013、017、021、025</t>
         </is>
       </c>
       <c r="F3" s="8" t="inlineStr">
@@ -2392,7 +2240,7 @@
       </c>
       <c r="I3" s="8" t="inlineStr">
         <is>
-          <t>本片复用 7 镜；一次下满，顺着「相似推荐」滚雪球，风格天然统一</t>
+          <t>本片复用 6 镜；一次下满，顺着「相似推荐」滚雪球，风格天然统一</t>
         </is>
       </c>
     </row>
@@ -2415,7 +2263,7 @@
       </c>
       <c r="E4" s="7" t="inlineStr">
         <is>
-          <t>006、010、014、018、022、026、030</t>
+          <t>006、010、014、018、022、026</t>
         </is>
       </c>
       <c r="F4" s="8" t="inlineStr">
@@ -2435,7 +2283,7 @@
       </c>
       <c r="I4" s="8" t="inlineStr">
         <is>
-          <t>本片复用 7 镜；一次下满，顺着「相似推荐」滚雪球，风格天然统一</t>
+          <t>本片复用 6 镜；一次下满，顺着「相似推荐」滚雪球，风格天然统一</t>
         </is>
       </c>
     </row>
@@ -2458,7 +2306,7 @@
       </c>
       <c r="E5" s="7" t="inlineStr">
         <is>
-          <t>003、007、011、015、019、023、027、031</t>
+          <t>003、007、011、015、019、023、027</t>
         </is>
       </c>
       <c r="F5" s="8" t="inlineStr">
@@ -2478,7 +2326,7 @@
       </c>
       <c r="I5" s="8" t="inlineStr">
         <is>
-          <t>本片复用 8 镜；一次下满，顺着「相似推荐」滚雪球，风格天然统一</t>
+          <t>本片复用 7 镜；一次下满，顺着「相似推荐」滚雪球，风格天然统一</t>
         </is>
       </c>
     </row>
@@ -2544,7 +2392,7 @@
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>007、031</t>
+          <t>006、028</t>
         </is>
       </c>
       <c r="F7" s="6" t="inlineStr">
@@ -2587,7 +2435,7 @@
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>032-033</t>
+          <t>029-030</t>
         </is>
       </c>
       <c r="F8" s="6" t="inlineStr">

--- a/workshop/da88ad747a.xlsx
+++ b/workshop/da88ad747a.xlsx
@@ -512,7 +512,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>问题类型：倒闭 / 关停　地区：江苏　内容价值：★92.5　总时长：70.6 秒　镜次：30</t>
+          <t>问题类型：倒闭 / 关停　地区：江苏　内容价值：★92.5　总时长：72.2 秒　镜次：30</t>
         </is>
       </c>
     </row>
@@ -747,14 +747,14 @@
         <v>4</v>
       </c>
       <c r="C8" s="7" t="n">
-        <v>6.5</v>
+        <v>5.2</v>
       </c>
       <c r="D8" s="7" t="n">
-        <v>2.5</v>
+        <v>1.2</v>
       </c>
       <c r="E8" s="8" t="inlineStr">
         <is>
-          <t>栽在「倒闭 / 关停」上</t>
+          <t>就这么倒下了</t>
         </is>
       </c>
       <c r="F8" s="7" t="inlineStr">
@@ -792,10 +792,10 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>6.5</v>
+        <v>5.2</v>
       </c>
       <c r="C9" s="7" t="n">
-        <v>8.1</v>
+        <v>6.8</v>
       </c>
       <c r="D9" s="7" t="n">
         <v>1.6</v>
@@ -840,10 +840,10 @@
         </is>
       </c>
       <c r="B10" s="7" t="n">
-        <v>8.1</v>
+        <v>6.8</v>
       </c>
       <c r="C10" s="7" t="n">
-        <v>11</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="D10" s="7" t="n">
         <v>2.9</v>
@@ -896,10 +896,10 @@
         </is>
       </c>
       <c r="B11" s="7" t="n">
-        <v>11</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="C11" s="7" t="n">
-        <v>14.4</v>
+        <v>13.1</v>
       </c>
       <c r="D11" s="7" t="n">
         <v>3.4</v>
@@ -944,10 +944,10 @@
         </is>
       </c>
       <c r="B12" s="7" t="n">
-        <v>14.4</v>
+        <v>13.1</v>
       </c>
       <c r="C12" s="7" t="n">
-        <v>17.3</v>
+        <v>16</v>
       </c>
       <c r="D12" s="7" t="n">
         <v>2.9</v>
@@ -992,10 +992,10 @@
         </is>
       </c>
       <c r="B13" s="7" t="n">
-        <v>17.3</v>
+        <v>16</v>
       </c>
       <c r="C13" s="7" t="n">
-        <v>19.1</v>
+        <v>17.8</v>
       </c>
       <c r="D13" s="7" t="n">
         <v>1.8</v>
@@ -1040,10 +1040,10 @@
         </is>
       </c>
       <c r="B14" s="7" t="n">
-        <v>19.1</v>
+        <v>17.8</v>
       </c>
       <c r="C14" s="7" t="n">
-        <v>20.9</v>
+        <v>19.6</v>
       </c>
       <c r="D14" s="7" t="n">
         <v>1.8</v>
@@ -1088,10 +1088,10 @@
         </is>
       </c>
       <c r="B15" s="7" t="n">
-        <v>20.9</v>
+        <v>19.6</v>
       </c>
       <c r="C15" s="7" t="n">
-        <v>23.4</v>
+        <v>22.1</v>
       </c>
       <c r="D15" s="7" t="n">
         <v>2.5</v>
@@ -1136,10 +1136,10 @@
         </is>
       </c>
       <c r="B16" s="7" t="n">
-        <v>23.4</v>
+        <v>22.1</v>
       </c>
       <c r="C16" s="7" t="n">
-        <v>25.3</v>
+        <v>24</v>
       </c>
       <c r="D16" s="7" t="n">
         <v>1.9</v>
@@ -1184,17 +1184,17 @@
         </is>
       </c>
       <c r="B17" s="7" t="n">
-        <v>25.3</v>
+        <v>24</v>
       </c>
       <c r="C17" s="7" t="n">
-        <v>27.4</v>
+        <v>25.9</v>
       </c>
       <c r="D17" s="7" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="E17" s="8" t="inlineStr">
         <is>
-          <t>本案的财务病灶很具体</t>
+          <t>问题出在哪，一句话</t>
         </is>
       </c>
       <c r="F17" s="7" t="inlineStr">
@@ -1232,17 +1232,17 @@
         </is>
       </c>
       <c r="B18" s="7" t="n">
-        <v>27.4</v>
+        <v>25.9</v>
       </c>
       <c r="C18" s="7" t="n">
-        <v>29.3</v>
+        <v>27.8</v>
       </c>
       <c r="D18" s="7" t="n">
         <v>1.9</v>
       </c>
       <c r="E18" s="8" t="inlineStr">
         <is>
-          <t>订单高度依赖大客户</t>
+          <t>单靠几个大客户养着</t>
         </is>
       </c>
       <c r="F18" s="7" t="inlineStr">
@@ -1280,17 +1280,17 @@
         </is>
       </c>
       <c r="B19" s="7" t="n">
-        <v>29.3</v>
+        <v>27.8</v>
       </c>
       <c r="C19" s="7" t="n">
-        <v>31.8</v>
+        <v>30.3</v>
       </c>
       <c r="D19" s="7" t="n">
         <v>2.5</v>
       </c>
       <c r="E19" s="8" t="inlineStr">
         <is>
-          <t>账期被拉长，成本刚性上升</t>
+          <t>账期越拖越长，成本还死贵</t>
         </is>
       </c>
       <c r="F19" s="7" t="inlineStr">
@@ -1328,17 +1328,17 @@
         </is>
       </c>
       <c r="B20" s="7" t="n">
-        <v>31.8</v>
+        <v>30.3</v>
       </c>
       <c r="C20" s="7" t="n">
-        <v>33.6</v>
+        <v>32.2</v>
       </c>
       <c r="D20" s="7" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="E20" s="8" t="inlineStr">
         <is>
-          <t>毛利被两头夹</t>
+          <t>利润被两头夹成纸片</t>
         </is>
       </c>
       <c r="F20" s="7" t="inlineStr">
@@ -1376,17 +1376,17 @@
         </is>
       </c>
       <c r="B21" s="7" t="n">
-        <v>33.6</v>
+        <v>32.2</v>
       </c>
       <c r="C21" s="7" t="n">
-        <v>36.3</v>
+        <v>34.9</v>
       </c>
       <c r="D21" s="7" t="n">
         <v>2.7</v>
       </c>
       <c r="E21" s="8" t="inlineStr">
         <is>
-          <t>把这家五金机械厂的账拆开看</t>
+          <t>把这家五金机械厂的账说人话</t>
         </is>
       </c>
       <c r="F21" s="7" t="inlineStr">
@@ -1424,17 +1424,17 @@
         </is>
       </c>
       <c r="B22" s="7" t="n">
-        <v>36.3</v>
+        <v>34.9</v>
       </c>
       <c r="C22" s="7" t="n">
-        <v>39.7</v>
+        <v>37.8</v>
       </c>
       <c r="D22" s="7" t="n">
-        <v>3.4</v>
+        <v>2.9</v>
       </c>
       <c r="E22" s="8" t="inlineStr">
         <is>
-          <t>倒闭极少突发，是现金循环周期被拉长</t>
+          <t>倒闭很少突然，都是钱慢慢流干</t>
         </is>
       </c>
       <c r="F22" s="7" t="inlineStr">
@@ -1472,17 +1472,17 @@
         </is>
       </c>
       <c r="B23" s="7" t="n">
-        <v>39.7</v>
+        <v>37.8</v>
       </c>
       <c r="C23" s="7" t="n">
-        <v>41.8</v>
+        <v>39.6</v>
       </c>
       <c r="D23" s="7" t="n">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="E23" s="8" t="inlineStr">
         <is>
-          <t>应收收不回，存货压钱</t>
+          <t>客户拖着货款不给</t>
         </is>
       </c>
       <c r="F23" s="7" t="inlineStr">
@@ -1520,17 +1520,17 @@
         </is>
       </c>
       <c r="B24" s="7" t="n">
-        <v>41.8</v>
+        <v>39.6</v>
       </c>
       <c r="C24" s="7" t="n">
-        <v>44.5</v>
+        <v>42.7</v>
       </c>
       <c r="D24" s="7" t="n">
-        <v>2.7</v>
+        <v>3.1</v>
       </c>
       <c r="E24" s="8" t="inlineStr">
         <is>
-          <t>扩产吞现金，三条管道同时漏</t>
+          <t>仓库货卖不掉，老板还借钱上新线</t>
         </is>
       </c>
       <c r="F24" s="7" t="inlineStr">
@@ -1568,17 +1568,17 @@
         </is>
       </c>
       <c r="B25" s="7" t="n">
-        <v>44.5</v>
+        <v>42.7</v>
       </c>
       <c r="C25" s="7" t="n">
-        <v>46.6</v>
+        <v>46.1</v>
       </c>
       <c r="D25" s="7" t="n">
-        <v>2.1</v>
+        <v>3.4</v>
       </c>
       <c r="E25" s="8" t="inlineStr">
         <is>
-          <t>安全垫撑不到回款那天</t>
+          <t>三条水管一起漏，家底撑不到回款那天就见了底</t>
         </is>
       </c>
       <c r="F25" s="7" t="inlineStr">
@@ -1616,17 +1616,17 @@
         </is>
       </c>
       <c r="B26" s="7" t="n">
-        <v>46.6</v>
+        <v>46.1</v>
       </c>
       <c r="C26" s="7" t="n">
-        <v>48.5</v>
+        <v>49.2</v>
       </c>
       <c r="D26" s="7" t="n">
-        <v>1.9</v>
+        <v>3.1</v>
       </c>
       <c r="E26" s="8" t="inlineStr">
         <is>
-          <t>看三数，安全垫月数</t>
+          <t>你只盯三个数，兜里钱够花几个月</t>
         </is>
       </c>
       <c r="F26" s="7" t="inlineStr">
@@ -1664,17 +1664,17 @@
         </is>
       </c>
       <c r="B27" s="7" t="n">
-        <v>48.5</v>
+        <v>49.2</v>
       </c>
       <c r="C27" s="7" t="n">
-        <v>51</v>
+        <v>52.5</v>
       </c>
       <c r="D27" s="7" t="n">
-        <v>2.5</v>
+        <v>3.3</v>
       </c>
       <c r="E27" s="8" t="inlineStr">
         <is>
-          <t>应收周转天数，资产负债率</t>
+          <t>客户拖你多少天，欠的钱是家底几倍</t>
         </is>
       </c>
       <c r="F27" s="7" t="inlineStr">
@@ -1712,10 +1712,10 @@
         </is>
       </c>
       <c r="B28" s="7" t="n">
-        <v>51</v>
+        <v>52.5</v>
       </c>
       <c r="C28" s="7" t="n">
-        <v>53.1</v>
+        <v>54.6</v>
       </c>
       <c r="D28" s="7" t="n">
         <v>2.1</v>
@@ -1760,10 +1760,10 @@
         </is>
       </c>
       <c r="B29" s="7" t="n">
-        <v>53.1</v>
+        <v>54.6</v>
       </c>
       <c r="C29" s="7" t="n">
-        <v>55.6</v>
+        <v>57.1</v>
       </c>
       <c r="D29" s="7" t="n">
         <v>2.5</v>
@@ -1808,10 +1808,10 @@
         </is>
       </c>
       <c r="B30" s="7" t="n">
-        <v>55.6</v>
+        <v>57.1</v>
       </c>
       <c r="C30" s="7" t="n">
-        <v>59.1</v>
+        <v>60.6</v>
       </c>
       <c r="D30" s="7" t="n">
         <v>3.5</v>
@@ -1864,10 +1864,10 @@
         </is>
       </c>
       <c r="B31" s="7" t="n">
-        <v>59.1</v>
+        <v>60.6</v>
       </c>
       <c r="C31" s="7" t="n">
-        <v>61.5</v>
+        <v>63</v>
       </c>
       <c r="D31" s="7" t="n">
         <v>2.4</v>
@@ -1920,17 +1920,17 @@
         </is>
       </c>
       <c r="B32" s="7" t="n">
-        <v>61.5</v>
+        <v>63</v>
       </c>
       <c r="C32" s="7" t="n">
-        <v>65.7</v>
+        <v>67.2</v>
       </c>
       <c r="D32" s="7" t="n">
         <v>4.2</v>
       </c>
       <c r="E32" s="8" t="inlineStr">
         <is>
-          <t>同类厂记住三件事，①留足 6 个月现金安全垫再扩张</t>
+          <t>同类厂记住三件事，①兜里先留够半年的活钱再扩张</t>
         </is>
       </c>
       <c r="F32" s="7" t="inlineStr">
@@ -1950,12 +1950,12 @@
       </c>
       <c r="I32" s="8" t="inlineStr">
         <is>
-          <t>数字上大字幕：6 个月</t>
+          <t>避坑清单上屏（≤3 条）</t>
         </is>
       </c>
       <c r="J32" s="7" t="inlineStr">
         <is>
-          <t>数字叮</t>
+          <t>结论咚</t>
         </is>
       </c>
       <c r="K32" s="7" t="inlineStr">
@@ -1976,17 +1976,17 @@
         </is>
       </c>
       <c r="B33" s="7" t="n">
-        <v>65.7</v>
+        <v>67.2</v>
       </c>
       <c r="C33" s="7" t="n">
-        <v>68.2</v>
+        <v>69.7</v>
       </c>
       <c r="D33" s="7" t="n">
         <v>2.5</v>
       </c>
       <c r="E33" s="8" t="inlineStr">
         <is>
-          <t>②砍掉不赚钱的低端红海单</t>
+          <t>②不赚钱的低价单该砍就砍</t>
         </is>
       </c>
       <c r="F33" s="7" t="inlineStr">
@@ -2032,17 +2032,17 @@
         </is>
       </c>
       <c r="B34" s="7" t="n">
-        <v>68.2</v>
+        <v>69.7</v>
       </c>
       <c r="C34" s="7" t="n">
-        <v>70.59999999999999</v>
+        <v>72.2</v>
       </c>
       <c r="D34" s="7" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="E34" s="8" t="inlineStr">
         <is>
-          <t>③每年固定比例投技改</t>
+          <t>③每年匀一笔钱搞技术升级</t>
         </is>
       </c>
       <c r="F34" s="7" t="inlineStr">
@@ -2392,7 +2392,7 @@
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>006、028</t>
+          <t>006</t>
         </is>
       </c>
       <c r="F7" s="6" t="inlineStr">
